--- a/excel/Ch08_Irrecoverable_Debts.xlsx
+++ b/excel/Ch08_Irrecoverable_Debts.xlsx
@@ -176,7 +176,7 @@
     <t xml:space="preserve">Year ended 31 December 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: Model Question 8.8 (Grace)</t>
+    <t xml:space="preserve">Practice: Model Question 8.11 (Grace)</t>
   </si>
   <si>
     <t xml:space="preserve">Type your answers in the yellow cells. The Check column marks them.</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">Grace keeps an allowance for irrecoverable debts. Year end 31 December.</t>
   </si>
   <si>
-    <t xml:space="preserve">Data (from Model Question 8.8)</t>
+    <t xml:space="preserve">Data (from Model Question 8.11)</t>
   </si>
   <si>
     <t xml:space="preserve">Debts to be written off</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">Your score (number correct)</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: Model Question 8.8 (Grace): Answers</t>
+    <t xml:space="preserve">Practice: Model Question 8.11 (Grace): Answers</t>
   </si>
   <si>
     <t xml:space="preserve">Every answer is a formula linked to the Practice sheet data.</t>
